--- a/lai ngan hang.xlsx
+++ b/lai ngan hang.xlsx
@@ -9,12 +9,12 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Năm</t>
   </si>
@@ -31,40 +31,35 @@
     <t>Lãi suất 5%/ 6 tháng</t>
   </si>
   <si>
-    <t>lãi suất ngân hàng 7%/ tháng</t>
-  </si>
-  <si>
     <t>Tháng</t>
   </si>
   <si>
     <t>&lt;=&gt; FX</t>
   </si>
   <si>
-    <t>~ 730 tr</t>
-  </si>
-  <si>
     <t>vốn khởi đầu</t>
   </si>
   <si>
     <t>Mỗi tháng bỏ 
-200USD trade ( 1 jack)</t>
+100USD trade ( 1/2 jack)</t>
   </si>
   <si>
-    <t>VNĐ</t>
+    <t>lãi 15% 1 tháng</t>
   </si>
   <si>
-    <t>3,76 tỉ</t>
+    <t>năm thứ 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">năm 5 </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="2">
     <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -122,12 +117,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -143,15 +137,13 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Comma" xfId="2" builtinId="3"/>
+  <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -455,7 +447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C5:J79"/>
+  <dimension ref="C4:J68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="26.140625" customWidth="1"/>
@@ -466,6 +458,7 @@
     <col min="10" max="10" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="4" spans="3:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="3:10" x14ac:dyDescent="0.25">
       <c r="D5" s="1" t="s">
         <v>3</v>
@@ -474,18 +467,18 @@
         <v>4</v>
       </c>
       <c r="F5" s="2"/>
-      <c r="H5" s="9" t="s">
-        <v>10</v>
+      <c r="H5" s="8" t="s">
+        <v>8</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="H6" s="8"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="3:10" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H6" s="9"/>
     </row>
     <row r="7" spans="3:10" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
@@ -498,7 +491,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="3:10" x14ac:dyDescent="0.25">
@@ -519,7 +512,7 @@
         <v>100</v>
       </c>
       <c r="I8" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="3:10" x14ac:dyDescent="0.25">
@@ -538,8 +531,8 @@
         <v>2</v>
       </c>
       <c r="H9" s="7">
-        <f xml:space="preserve"> H8 * 1.07 + 200</f>
-        <v>307</v>
+        <f xml:space="preserve"> H8 * 1.15 + 100</f>
+        <v>215</v>
       </c>
     </row>
     <row r="10" spans="3:10" x14ac:dyDescent="0.25">
@@ -551,15 +544,15 @@
         <v>94575000</v>
       </c>
       <c r="E10" s="5">
-        <f t="shared" ref="E10:E73" si="1">D10 + D10*0.05</f>
+        <f t="shared" ref="E10:E43" si="1">D10 + D10*0.05</f>
         <v>99303750</v>
       </c>
       <c r="G10">
         <v>3</v>
       </c>
       <c r="H10" s="7">
-        <f xml:space="preserve"> H9 * 1.07 + 200</f>
-        <v>528.49</v>
+        <f t="shared" ref="H10:H43" si="2" xml:space="preserve"> H9 * 1.15 + 100</f>
+        <v>347.25</v>
       </c>
     </row>
     <row r="11" spans="3:10" x14ac:dyDescent="0.25">
@@ -578,8 +571,8 @@
         <v>4</v>
       </c>
       <c r="H11" s="7">
-        <f t="shared" ref="H11:H74" si="2" xml:space="preserve"> H10 * 1.07 + 200</f>
-        <v>765.48430000000008</v>
+        <f t="shared" si="2"/>
+        <v>499.33749999999998</v>
       </c>
     </row>
     <row r="12" spans="3:10" x14ac:dyDescent="0.25">
@@ -599,7 +592,7 @@
       </c>
       <c r="H12" s="7">
         <f t="shared" si="2"/>
-        <v>1019.0682010000002</v>
+        <v>674.23812499999997</v>
       </c>
     </row>
     <row r="13" spans="3:10" x14ac:dyDescent="0.25">
@@ -619,7 +612,7 @@
       </c>
       <c r="H13" s="7">
         <f t="shared" si="2"/>
-        <v>1290.4029750700001</v>
+        <v>875.37384374999988</v>
       </c>
     </row>
     <row r="14" spans="3:10" x14ac:dyDescent="0.25">
@@ -639,7 +632,7 @@
       </c>
       <c r="H14" s="7">
         <f t="shared" si="2"/>
-        <v>1580.7311833249003</v>
+        <v>1106.6799203124997</v>
       </c>
     </row>
     <row r="15" spans="3:10" x14ac:dyDescent="0.25">
@@ -659,7 +652,7 @@
       </c>
       <c r="H15" s="7">
         <f t="shared" si="2"/>
-        <v>1891.3823661576434</v>
+        <v>1372.6819083593746</v>
       </c>
     </row>
     <row r="16" spans="3:10" x14ac:dyDescent="0.25">
@@ -679,7 +672,7 @@
       </c>
       <c r="H16" s="7">
         <f t="shared" si="2"/>
-        <v>2223.7791317886786</v>
+        <v>1678.5841946132807</v>
       </c>
     </row>
     <row r="17" spans="3:8" x14ac:dyDescent="0.25">
@@ -699,7 +692,7 @@
       </c>
       <c r="H17" s="7">
         <f t="shared" si="2"/>
-        <v>2579.4436710138862</v>
+        <v>2030.3718238052727</v>
       </c>
     </row>
     <row r="18" spans="3:8" x14ac:dyDescent="0.25">
@@ -719,7 +712,7 @@
       </c>
       <c r="H18" s="7">
         <f t="shared" si="2"/>
-        <v>2960.0047279848582</v>
+        <v>2434.9275973760632</v>
       </c>
     </row>
     <row r="19" spans="3:8" x14ac:dyDescent="0.25">
@@ -739,7 +732,7 @@
       </c>
       <c r="H19" s="7">
         <f t="shared" si="2"/>
-        <v>3367.2050589437986</v>
+        <v>2900.1667369824727</v>
       </c>
     </row>
     <row r="20" spans="3:8" x14ac:dyDescent="0.25">
@@ -759,7 +752,7 @@
       </c>
       <c r="H20" s="7">
         <f t="shared" si="2"/>
-        <v>3802.9094130698645</v>
+        <v>3435.1917475298433</v>
       </c>
     </row>
     <row r="21" spans="3:8" x14ac:dyDescent="0.25">
@@ -779,7 +772,7 @@
       </c>
       <c r="H21" s="7">
         <f t="shared" si="2"/>
-        <v>4269.1130719847552</v>
+        <v>4050.4705096593193</v>
       </c>
     </row>
     <row r="22" spans="3:8" x14ac:dyDescent="0.25">
@@ -799,7 +792,7 @@
       </c>
       <c r="H22" s="7">
         <f t="shared" si="2"/>
-        <v>4767.950987023688</v>
+        <v>4758.0410861082164</v>
       </c>
     </row>
     <row r="23" spans="3:8" x14ac:dyDescent="0.25">
@@ -819,7 +812,7 @@
       </c>
       <c r="H23" s="7">
         <f t="shared" si="2"/>
-        <v>5301.7075561153461</v>
+        <v>5571.7472490244481</v>
       </c>
     </row>
     <row r="24" spans="3:8" x14ac:dyDescent="0.25">
@@ -839,7 +832,7 @@
       </c>
       <c r="H24" s="7">
         <f t="shared" si="2"/>
-        <v>5872.827085043421</v>
+        <v>6507.5093363781152</v>
       </c>
     </row>
     <row r="25" spans="3:8" x14ac:dyDescent="0.25">
@@ -859,7 +852,7 @@
       </c>
       <c r="H25" s="7">
         <f t="shared" si="2"/>
-        <v>6483.9249809964613</v>
+        <v>7583.6357368348317</v>
       </c>
     </row>
     <row r="26" spans="3:8" x14ac:dyDescent="0.25">
@@ -879,7 +872,7 @@
       </c>
       <c r="H26" s="7">
         <f t="shared" si="2"/>
-        <v>7137.7997296662143</v>
+        <v>8821.181097360055</v>
       </c>
     </row>
     <row r="27" spans="3:8" x14ac:dyDescent="0.25">
@@ -899,7 +892,7 @@
       </c>
       <c r="H27" s="7">
         <f t="shared" si="2"/>
-        <v>7837.4457107428498</v>
+        <v>10244.358261964062</v>
       </c>
     </row>
     <row r="28" spans="3:8" x14ac:dyDescent="0.25">
@@ -919,7 +912,7 @@
       </c>
       <c r="H28" s="7">
         <f t="shared" si="2"/>
-        <v>8586.0669104948502</v>
+        <v>11881.01200125867</v>
       </c>
     </row>
     <row r="29" spans="3:8" x14ac:dyDescent="0.25">
@@ -939,7 +932,7 @@
       </c>
       <c r="H29" s="7">
         <f t="shared" si="2"/>
-        <v>9387.0915942294905</v>
+        <v>13763.16380144747</v>
       </c>
     </row>
     <row r="30" spans="3:8" x14ac:dyDescent="0.25">
@@ -959,7 +952,7 @@
       </c>
       <c r="H30" s="7">
         <f t="shared" si="2"/>
-        <v>10244.188005825556</v>
+        <v>15927.638371664589</v>
       </c>
     </row>
     <row r="31" spans="3:8" x14ac:dyDescent="0.25">
@@ -979,7 +972,7 @@
       </c>
       <c r="H31" s="7">
         <f t="shared" si="2"/>
-        <v>11161.281166233344</v>
+        <v>18416.784127414274</v>
       </c>
     </row>
     <row r="32" spans="3:8" x14ac:dyDescent="0.25">
@@ -999,7 +992,7 @@
       </c>
       <c r="H32" s="7">
         <f t="shared" si="2"/>
-        <v>12142.57084786968</v>
+        <v>21279.301746526413</v>
       </c>
     </row>
     <row r="33" spans="3:9" x14ac:dyDescent="0.25">
@@ -1019,7 +1012,7 @@
       </c>
       <c r="H33" s="7">
         <f t="shared" si="2"/>
-        <v>13192.550807220558</v>
+        <v>24571.197008505373</v>
       </c>
     </row>
     <row r="34" spans="3:9" x14ac:dyDescent="0.25">
@@ -1039,7 +1032,7 @@
       </c>
       <c r="H34" s="7">
         <f t="shared" si="2"/>
-        <v>14316.029363725997</v>
+        <v>28356.876559781176</v>
       </c>
     </row>
     <row r="35" spans="3:9" x14ac:dyDescent="0.25">
@@ -1059,7 +1052,7 @@
       </c>
       <c r="H35" s="7">
         <f t="shared" si="2"/>
-        <v>15518.151419186817</v>
+        <v>32710.40804374835</v>
       </c>
     </row>
     <row r="36" spans="3:9" x14ac:dyDescent="0.25">
@@ -1079,7 +1072,7 @@
       </c>
       <c r="H36" s="7">
         <f t="shared" si="2"/>
-        <v>16804.422018529895</v>
+        <v>37716.969250310598</v>
       </c>
     </row>
     <row r="37" spans="3:9" x14ac:dyDescent="0.25">
@@ -1099,7 +1092,7 @@
       </c>
       <c r="H37" s="7">
         <f t="shared" si="2"/>
-        <v>18180.731559826989</v>
+        <v>43474.514637857181</v>
       </c>
     </row>
     <row r="38" spans="3:9" x14ac:dyDescent="0.25">
@@ -1119,7 +1112,7 @@
       </c>
       <c r="H38" s="7">
         <f t="shared" si="2"/>
-        <v>19653.382769014879</v>
+        <v>50095.691833535755</v>
       </c>
     </row>
     <row r="39" spans="3:9" x14ac:dyDescent="0.25">
@@ -1139,7 +1132,7 @@
       </c>
       <c r="H39" s="7">
         <f t="shared" si="2"/>
-        <v>21229.119562845921</v>
+        <v>57710.045608566114</v>
       </c>
     </row>
     <row r="40" spans="3:9" x14ac:dyDescent="0.25">
@@ -1159,7 +1152,7 @@
       </c>
       <c r="H40" s="7">
         <f t="shared" si="2"/>
-        <v>22915.157932245136</v>
+        <v>66466.55244985102</v>
       </c>
     </row>
     <row r="41" spans="3:9" x14ac:dyDescent="0.25">
@@ -1167,7 +1160,7 @@
         <v>34</v>
       </c>
       <c r="D41" s="5">
-        <f t="shared" ref="D41:D71" si="3">E40 + 30000000</f>
+        <f t="shared" ref="D41:D43" si="3">E40 + 30000000</f>
         <v>2552008781.4812851</v>
       </c>
       <c r="E41" s="5">
@@ -1179,7 +1172,7 @@
       </c>
       <c r="H41" s="7">
         <f t="shared" si="2"/>
-        <v>24719.218987502296</v>
+        <v>76536.535317328671</v>
       </c>
     </row>
     <row r="42" spans="3:9" x14ac:dyDescent="0.25">
@@ -1199,7 +1192,7 @@
       </c>
       <c r="H42" s="7">
         <f t="shared" si="2"/>
-        <v>26649.564316627457</v>
+        <v>88117.015614927965</v>
       </c>
     </row>
     <row r="43" spans="3:9" x14ac:dyDescent="0.25">
@@ -1219,10 +1212,10 @@
       </c>
       <c r="H43" s="7">
         <f t="shared" si="2"/>
-        <v>28715.03381879138</v>
+        <v>101434.56795716715</v>
       </c>
       <c r="I43" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="3:9" x14ac:dyDescent="0.25">
@@ -1230,19 +1223,19 @@
         <v>37</v>
       </c>
       <c r="D44" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="D44:D68" si="4">E43 + 30000000</f>
         <v>3048844165.6622729</v>
       </c>
       <c r="E44" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="E44:E68" si="5">D44 + D44*0.05</f>
         <v>3201286373.9453864</v>
       </c>
       <c r="G44">
         <v>37</v>
       </c>
       <c r="H44" s="7">
-        <f t="shared" si="2"/>
-        <v>30925.086186106779</v>
+        <f t="shared" ref="H44:H68" si="6" xml:space="preserve"> H43 * 1.15 + 100</f>
+        <v>116749.75315074221</v>
       </c>
     </row>
     <row r="45" spans="3:9" x14ac:dyDescent="0.25">
@@ -1250,19 +1243,19 @@
         <v>38</v>
       </c>
       <c r="D45" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3231286373.9453864</v>
       </c>
       <c r="E45" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>3392850692.6426558</v>
       </c>
-      <c r="G45">
+      <c r="G45" s="4">
         <v>38</v>
       </c>
       <c r="H45" s="7">
-        <f t="shared" si="2"/>
-        <v>33289.842219134254</v>
+        <f t="shared" si="6"/>
+        <v>134362.21612335354</v>
       </c>
     </row>
     <row r="46" spans="3:9" x14ac:dyDescent="0.25">
@@ -1270,39 +1263,39 @@
         <v>39</v>
       </c>
       <c r="D46" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3422850692.6426558</v>
       </c>
       <c r="E46" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>3593993227.2747889</v>
       </c>
       <c r="G46">
         <v>39</v>
       </c>
       <c r="H46" s="7">
-        <f t="shared" si="2"/>
-        <v>35820.131174473652</v>
+        <f t="shared" si="6"/>
+        <v>154616.54854185655</v>
       </c>
     </row>
     <row r="47" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C47" s="4">
+      <c r="C47">
         <v>40</v>
       </c>
       <c r="D47" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3623993227.2747889</v>
       </c>
       <c r="E47" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>3805192888.6385283</v>
       </c>
-      <c r="G47">
+      <c r="G47" s="4">
         <v>40</v>
       </c>
       <c r="H47" s="7">
-        <f t="shared" si="2"/>
-        <v>38527.540356686812</v>
+        <f t="shared" si="6"/>
+        <v>177909.03082313502</v>
       </c>
     </row>
     <row r="48" spans="3:9" x14ac:dyDescent="0.25">
@@ -1310,19 +1303,19 @@
         <v>41</v>
       </c>
       <c r="D48" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3835192888.6385283</v>
       </c>
       <c r="E48" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>4026952533.0704546</v>
       </c>
       <c r="G48">
         <v>41</v>
       </c>
       <c r="H48" s="7">
-        <f t="shared" si="2"/>
-        <v>41424.468181654891</v>
+        <f t="shared" si="6"/>
+        <v>204695.38544660527</v>
       </c>
     </row>
     <row r="49" spans="3:8" x14ac:dyDescent="0.25">
@@ -1330,19 +1323,19 @@
         <v>42</v>
       </c>
       <c r="D49" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4056952533.0704546</v>
       </c>
       <c r="E49" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>4259800159.7239771</v>
       </c>
-      <c r="G49">
+      <c r="G49" s="4">
         <v>42</v>
       </c>
       <c r="H49" s="7">
-        <f t="shared" si="2"/>
-        <v>44524.180954370735</v>
+        <f t="shared" si="6"/>
+        <v>235499.69326359604</v>
       </c>
     </row>
     <row r="50" spans="3:8" x14ac:dyDescent="0.25">
@@ -1350,19 +1343,19 @@
         <v>43</v>
       </c>
       <c r="D50" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4289800159.7239771</v>
       </c>
       <c r="E50" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>4504290167.7101755</v>
       </c>
       <c r="G50">
         <v>43</v>
       </c>
       <c r="H50" s="7">
-        <f t="shared" si="2"/>
-        <v>47840.873621176688</v>
+        <f t="shared" si="6"/>
+        <v>270924.64725313545</v>
       </c>
     </row>
     <row r="51" spans="3:8" x14ac:dyDescent="0.25">
@@ -1370,19 +1363,19 @@
         <v>44</v>
       </c>
       <c r="D51" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4534290167.7101755</v>
       </c>
       <c r="E51" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>4761004676.0956841</v>
       </c>
-      <c r="G51">
+      <c r="G51" s="4">
         <v>44</v>
       </c>
       <c r="H51" s="7">
-        <f t="shared" si="2"/>
-        <v>51389.73477465906</v>
+        <f t="shared" si="6"/>
+        <v>311663.34434110572</v>
       </c>
     </row>
     <row r="52" spans="3:8" x14ac:dyDescent="0.25">
@@ -1390,19 +1383,19 @@
         <v>45</v>
       </c>
       <c r="D52" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4791004676.0956841</v>
       </c>
       <c r="E52" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>5030554909.9004679</v>
       </c>
       <c r="G52">
         <v>45</v>
       </c>
       <c r="H52" s="7">
-        <f t="shared" si="2"/>
-        <v>55187.016208885201</v>
+        <f t="shared" si="6"/>
+        <v>358512.84599227156</v>
       </c>
     </row>
     <row r="53" spans="3:8" x14ac:dyDescent="0.25">
@@ -1410,19 +1403,19 @@
         <v>46</v>
       </c>
       <c r="D53" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5060554909.9004679</v>
       </c>
       <c r="E53" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>5313582655.3954916</v>
       </c>
-      <c r="G53">
+      <c r="G53" s="4">
         <v>46</v>
       </c>
       <c r="H53" s="7">
-        <f t="shared" si="2"/>
-        <v>59250.107343507167</v>
+        <f t="shared" si="6"/>
+        <v>412389.77289111225</v>
       </c>
     </row>
     <row r="54" spans="3:8" x14ac:dyDescent="0.25">
@@ -1430,19 +1423,19 @@
         <v>47</v>
       </c>
       <c r="D54" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5343582655.3954916</v>
       </c>
       <c r="E54" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>5610761788.165266</v>
       </c>
       <c r="G54">
         <v>47</v>
       </c>
       <c r="H54" s="7">
-        <f t="shared" si="2"/>
-        <v>63597.614857552675</v>
+        <f t="shared" si="6"/>
+        <v>474348.23882477905</v>
       </c>
     </row>
     <row r="55" spans="3:8" x14ac:dyDescent="0.25">
@@ -1450,19 +1443,19 @@
         <v>48</v>
       </c>
       <c r="D55" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5640761788.165266</v>
       </c>
       <c r="E55" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>5922799877.5735292</v>
       </c>
       <c r="G55" s="4">
         <v>48</v>
       </c>
       <c r="H55" s="7">
-        <f t="shared" si="2"/>
-        <v>68249.447897581369</v>
+        <f t="shared" si="6"/>
+        <v>545600.4746484959</v>
       </c>
     </row>
     <row r="56" spans="3:8" x14ac:dyDescent="0.25">
@@ -1470,39 +1463,39 @@
         <v>49</v>
       </c>
       <c r="D56" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>5952799877.5735292</v>
       </c>
       <c r="E56" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>6250439871.4522057</v>
       </c>
       <c r="G56">
         <v>49</v>
       </c>
       <c r="H56" s="7">
-        <f t="shared" si="2"/>
-        <v>73226.909250412064</v>
+        <f t="shared" si="6"/>
+        <v>627540.54584577028</v>
       </c>
     </row>
     <row r="57" spans="3:8" x14ac:dyDescent="0.25">
-      <c r="C57" s="4">
+      <c r="C57">
         <v>50</v>
       </c>
       <c r="D57" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6280439871.4522057</v>
       </c>
       <c r="E57" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>6594461865.0248156</v>
       </c>
-      <c r="G57">
+      <c r="G57" s="4">
         <v>50</v>
       </c>
       <c r="H57" s="7">
-        <f t="shared" si="2"/>
-        <v>78552.792897940919</v>
+        <f t="shared" si="6"/>
+        <v>721771.62772263575</v>
       </c>
     </row>
     <row r="58" spans="3:8" x14ac:dyDescent="0.25">
@@ -1510,19 +1503,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6624461865.0248156</v>
       </c>
       <c r="E58" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>6955684958.2760563</v>
       </c>
       <c r="G58">
         <v>51</v>
       </c>
       <c r="H58" s="7">
-        <f t="shared" si="2"/>
-        <v>84251.488400796792</v>
+        <f t="shared" si="6"/>
+        <v>830137.37188103108</v>
       </c>
     </row>
     <row r="59" spans="3:8" x14ac:dyDescent="0.25">
@@ -1530,19 +1523,19 @@
         <v>52</v>
       </c>
       <c r="D59" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>6985684958.2760563</v>
       </c>
       <c r="E59" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>7334969206.1898594</v>
       </c>
-      <c r="G59">
+      <c r="G59" s="4">
         <v>52</v>
       </c>
       <c r="H59" s="7">
-        <f t="shared" si="2"/>
-        <v>90349.092588852567</v>
+        <f t="shared" si="6"/>
+        <v>954757.97766318568</v>
       </c>
     </row>
     <row r="60" spans="3:8" x14ac:dyDescent="0.25">
@@ -1550,19 +1543,19 @@
         <v>53</v>
       </c>
       <c r="D60" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7364969206.1898594</v>
       </c>
       <c r="E60" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>7733217666.4993525</v>
       </c>
       <c r="G60">
         <v>53</v>
       </c>
       <c r="H60" s="7">
-        <f t="shared" si="2"/>
-        <v>96873.529070072254</v>
+        <f t="shared" si="6"/>
+        <v>1098071.6743126635</v>
       </c>
     </row>
     <row r="61" spans="3:8" x14ac:dyDescent="0.25">
@@ -1570,19 +1563,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>7763217666.4993525</v>
       </c>
       <c r="E61" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>8151378549.8243198</v>
       </c>
-      <c r="G61">
+      <c r="G61" s="4">
         <v>54</v>
       </c>
       <c r="H61" s="7">
-        <f t="shared" si="2"/>
-        <v>103854.67610497732</v>
+        <f t="shared" si="6"/>
+        <v>1262882.425459563</v>
       </c>
     </row>
     <row r="62" spans="3:8" x14ac:dyDescent="0.25">
@@ -1590,19 +1583,19 @@
         <v>55</v>
       </c>
       <c r="D62" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8181378549.8243198</v>
       </c>
       <c r="E62" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>8590447477.3155365</v>
       </c>
       <c r="G62">
         <v>55</v>
       </c>
       <c r="H62" s="7">
-        <f t="shared" si="2"/>
-        <v>111324.50343232574</v>
+        <f t="shared" si="6"/>
+        <v>1452414.7892784975</v>
       </c>
     </row>
     <row r="63" spans="3:8" x14ac:dyDescent="0.25">
@@ -1610,19 +1603,19 @@
         <v>56</v>
       </c>
       <c r="D63" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>8620447477.3155365</v>
       </c>
       <c r="E63" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>9051469851.1813126</v>
       </c>
-      <c r="G63">
+      <c r="G63" s="4">
         <v>56</v>
       </c>
       <c r="H63" s="7">
-        <f t="shared" si="2"/>
-        <v>119317.21867258855</v>
+        <f t="shared" si="6"/>
+        <v>1670377.0076702719</v>
       </c>
     </row>
     <row r="64" spans="3:8" x14ac:dyDescent="0.25">
@@ -1630,306 +1623,102 @@
         <v>57</v>
       </c>
       <c r="D64" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9081469851.1813126</v>
       </c>
       <c r="E64" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>9535543343.7403774</v>
       </c>
       <c r="G64">
         <v>57</v>
       </c>
       <c r="H64" s="7">
-        <f t="shared" si="2"/>
-        <v>127869.42397966977</v>
-      </c>
-    </row>
-    <row r="65" spans="3:10" x14ac:dyDescent="0.25">
+        <f t="shared" si="6"/>
+        <v>1921033.5588208125</v>
+      </c>
+    </row>
+    <row r="65" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C65">
         <v>58</v>
       </c>
       <c r="D65" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>9565543343.7403774</v>
       </c>
       <c r="E65" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>10043820510.927397</v>
       </c>
-      <c r="G65">
+      <c r="G65" s="4">
         <v>58</v>
       </c>
       <c r="H65" s="7">
-        <f t="shared" si="2"/>
-        <v>137020.28365824666</v>
-      </c>
-    </row>
-    <row r="66" spans="3:10" x14ac:dyDescent="0.25">
+        <f t="shared" si="6"/>
+        <v>2209288.5926439343</v>
+      </c>
+    </row>
+    <row r="66" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C66">
         <v>59</v>
       </c>
       <c r="D66" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>10073820510.927397</v>
       </c>
       <c r="E66" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>10577511536.473766</v>
       </c>
       <c r="G66">
         <v>59</v>
       </c>
       <c r="H66" s="7">
-        <f t="shared" si="2"/>
-        <v>146811.70351432392</v>
-      </c>
-    </row>
-    <row r="67" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C67" s="4">
+        <f t="shared" si="6"/>
+        <v>2540781.8815405243</v>
+      </c>
+    </row>
+    <row r="67" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C67">
         <v>60</v>
       </c>
       <c r="D67" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>10607511536.473766</v>
       </c>
       <c r="E67" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>11137887113.297455</v>
       </c>
       <c r="G67" s="4">
         <v>60</v>
       </c>
       <c r="H67" s="7">
-        <f t="shared" si="2"/>
-        <v>157288.5227603266</v>
+        <f t="shared" si="6"/>
+        <v>2921999.1637716028</v>
       </c>
       <c r="I67" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="68" spans="3:10" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C68">
         <v>61</v>
       </c>
       <c r="D68" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>11167887113.297455</v>
       </c>
       <c r="E68" s="5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="5"/>
         <v>11726281468.962328</v>
       </c>
       <c r="G68">
         <v>61</v>
       </c>
       <c r="H68" s="7">
-        <f t="shared" si="2"/>
-        <v>168498.71935354947</v>
-      </c>
-    </row>
-    <row r="69" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C69">
-        <v>62</v>
-      </c>
-      <c r="D69" s="5">
-        <f t="shared" si="3"/>
-        <v>11756281468.962328</v>
-      </c>
-      <c r="E69" s="5">
-        <f t="shared" si="1"/>
-        <v>12344095542.410444</v>
-      </c>
-      <c r="G69">
-        <v>62</v>
-      </c>
-      <c r="H69" s="7">
-        <f t="shared" si="2"/>
-        <v>180493.62970829796</v>
-      </c>
-    </row>
-    <row r="70" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C70">
-        <v>63</v>
-      </c>
-      <c r="D70" s="5">
-        <f t="shared" si="3"/>
-        <v>12374095542.410444</v>
-      </c>
-      <c r="E70" s="5">
-        <f t="shared" si="1"/>
-        <v>12992800319.530966</v>
-      </c>
-      <c r="G70">
-        <v>63</v>
-      </c>
-      <c r="H70" s="7">
-        <f t="shared" si="2"/>
-        <v>193328.18378787884</v>
-      </c>
-    </row>
-    <row r="71" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C71">
-        <v>64</v>
-      </c>
-      <c r="D71" s="5">
-        <f>E70 + 30000000</f>
-        <v>13022800319.530966</v>
-      </c>
-      <c r="E71" s="5">
-        <f t="shared" si="1"/>
-        <v>13673940335.507515</v>
-      </c>
-      <c r="G71">
-        <v>64</v>
-      </c>
-      <c r="H71" s="7">
-        <f t="shared" si="2"/>
-        <v>207061.15665303037</v>
-      </c>
-    </row>
-    <row r="72" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C72">
-        <v>65</v>
-      </c>
-      <c r="D72" s="5">
-        <f>E71 + 30000000</f>
-        <v>13703940335.507515</v>
-      </c>
-      <c r="E72" s="5">
-        <f t="shared" si="1"/>
-        <v>14389137352.28289</v>
-      </c>
-      <c r="G72">
-        <v>65</v>
-      </c>
-      <c r="H72" s="7">
-        <f t="shared" si="2"/>
-        <v>221755.43761874249</v>
-      </c>
-    </row>
-    <row r="73" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C73">
-        <v>66</v>
-      </c>
-      <c r="D73" s="5">
-        <f>E72 + 30000000</f>
-        <v>14419137352.28289</v>
-      </c>
-      <c r="E73" s="5">
-        <f t="shared" si="1"/>
-        <v>15140094219.897036</v>
-      </c>
-      <c r="G73">
-        <v>66</v>
-      </c>
-      <c r="H73" s="7">
-        <f t="shared" si="2"/>
-        <v>237478.31825205448</v>
-      </c>
-    </row>
-    <row r="74" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C74">
-        <v>67</v>
-      </c>
-      <c r="D74" s="5">
-        <f>E73 + 30000000</f>
-        <v>15170094219.897036</v>
-      </c>
-      <c r="E74" s="5">
-        <f t="shared" ref="E74:E77" si="4">D74 + D74*0.05</f>
-        <v>15928598930.891888</v>
-      </c>
-      <c r="G74">
-        <v>67</v>
-      </c>
-      <c r="H74" s="7">
-        <f t="shared" si="2"/>
-        <v>254301.80052969832</v>
-      </c>
-    </row>
-    <row r="75" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C75">
-        <v>68</v>
-      </c>
-      <c r="D75" s="5">
-        <f>E74 + 30000000</f>
-        <v>15958598930.891888</v>
-      </c>
-      <c r="E75" s="5">
-        <f t="shared" si="4"/>
-        <v>16756528877.436481</v>
-      </c>
-      <c r="G75">
-        <v>68</v>
-      </c>
-      <c r="H75" s="7">
-        <f t="shared" ref="H75:H79" si="5" xml:space="preserve"> H74 * 1.07 + 200</f>
-        <v>272302.92656677723</v>
-      </c>
-    </row>
-    <row r="76" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C76">
-        <v>69</v>
-      </c>
-      <c r="D76" s="5">
-        <f>E75 + 30000000</f>
-        <v>16786528877.436481</v>
-      </c>
-      <c r="E76" s="5">
-        <f t="shared" si="4"/>
-        <v>17625855321.308304</v>
-      </c>
-      <c r="G76">
-        <v>69</v>
-      </c>
-      <c r="H76" s="7">
-        <f t="shared" si="5"/>
-        <v>291564.13142645167</v>
-      </c>
-    </row>
-    <row r="77" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="C77" s="4">
-        <v>70</v>
-      </c>
-      <c r="D77" s="5">
-        <f>E76 + 30000000</f>
-        <v>17655855321.308304</v>
-      </c>
-      <c r="E77" s="5">
-        <f t="shared" si="4"/>
-        <v>18538648087.373718</v>
-      </c>
-      <c r="G77">
-        <v>70</v>
-      </c>
-      <c r="H77" s="7">
-        <f t="shared" si="5"/>
-        <v>312173.62062630331</v>
-      </c>
-    </row>
-    <row r="78" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="G78">
-        <v>71</v>
-      </c>
-      <c r="H78" s="7">
-        <f t="shared" si="5"/>
-        <v>334225.77407014457</v>
-      </c>
-    </row>
-    <row r="79" spans="3:10" x14ac:dyDescent="0.25">
-      <c r="G79" s="4">
-        <v>72</v>
-      </c>
-      <c r="H79" s="7">
-        <f t="shared" si="5"/>
-        <v>357821.57825505472</v>
-      </c>
-      <c r="I79" s="10">
-        <v>8555182400</v>
-      </c>
-      <c r="J79" t="s">
-        <v>11</v>
+        <f t="shared" si="6"/>
+        <v>3360399.0383373429</v>
       </c>
     </row>
   </sheetData>
